--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>31.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>243.</t>
+          <t>250.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31.</t>
+          <t>64.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -533,64 +533,6 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Uttarakhand eTenders</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>25</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>250.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 09:00 AM</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>15-Jun-2026 02:00 PM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>15-Jun-2026 03:00 PM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[Construction of Chief Engineer (Distribution) Garhwal Zone, Office Building and Other Misc. Civil Works at 18 E.C. Road, UPCL Campus, Dehradun.] [ECC-17/2026-27][2026_UPCL8_96394_1]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>MD - UPCL||CE (Civil)||SE (Civil)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1,20,79,891</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>12079891</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SnkkmSbr53KLUrrNIrRVrNQ%3D%3D</t>
         </is>
       </c>
     </row>

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>64.</t>
+          <t>95.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>95.</t>
+          <t>129.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>129.</t>
+          <t>244.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>244.</t>
+          <t>265.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>265.</t>
+          <t>312.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,43 +494,101 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>312.</t>
+          <t>8.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>22-Jun-2026 04:15 PM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 03:30 PM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4,50,46,000</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>45046000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Uttarakhand eTenders</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>333.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>12-Jun-2026 04:15 PM</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>30-Jun-2026 12:30 PM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2,91,40,100</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K3" t="n">
         <v>29140100</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
         </is>

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.</t>
+          <t>24.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>333.</t>
+          <t>348.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>134.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>348.</t>
+          <t>420.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/uttarakhand_etenders.xlsx
+++ b/uttarakhand_etenders.xlsx
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -490,11 +490,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>134.</t>
+          <t>261.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,49 +548,49 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>420.</t>
+          <t>214.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:15 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Jun-2026 12:30 PM</t>
+          <t>08-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>09-Jul-2026 12:30 PM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
+          <t>[Construction work of restaurant and community centre under Vibrant Village in village Rongkong of development block Dharchula] [329 DATED 23-06-2026][2026_RES_96930_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
+          <t>RES - Chief Engineer||SE - Pithoragarh</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2,91,40,100</t>
+          <t>2,84,90,000</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>29140100</v>
+        <v>28490000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScuXPTCf2qgSeP5Ho2OAWPQ%3D%3D</t>
         </is>
       </c>
     </row>
